--- a/测试/恒流源测试/测试记录与分析/测试数据03.xlsx
+++ b/测试/恒流源测试/测试记录与分析/测试数据03.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS\University\电赛\26校内赛\NC-Current-Source\测试\恒流源测试\测试记录与分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E7C8090-0AC6-4A6E-9071-960B91C0B520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729CE362-354B-4B2E-8265-27A949C7C628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C77B3E43-BF6E-4A5B-B225-69B2FEFE6C14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C77B3E43-BF6E-4A5B-B225-69B2FEFE6C14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>VOUTP_raw</t>
   </si>
@@ -53,6 +54,10 @@
   </si>
   <si>
     <t>Iset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deltaI(Imeas-Idisp)_mA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -505,4 +510,175 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC104C84-FDC6-4891-884A-A9B4461F0949}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.4140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>40</v>
+      </c>
+      <c r="B6">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>50</v>
+      </c>
+      <c r="B7">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>60</v>
+      </c>
+      <c r="B8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>70</v>
+      </c>
+      <c r="B9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>80</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>90</v>
+      </c>
+      <c r="B11">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>150</v>
+      </c>
+      <c r="B13">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>200</v>
+      </c>
+      <c r="B14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>250</v>
+      </c>
+      <c r="B15">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>300</v>
+      </c>
+      <c r="B16">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>350</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>400</v>
+      </c>
+      <c r="B18">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>450</v>
+      </c>
+      <c r="B19">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>500</v>
+      </c>
+      <c r="B20">
+        <v>-0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>